--- a/实盘/实盘.xlsx
+++ b/实盘/实盘.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="105" windowWidth="12765" windowHeight="5715"/>
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -19,6 +19,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
+    <author>ray chen</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0">
@@ -108,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="BH8" authorId="1">
       <text>
         <r>
           <rPr>
@@ -171,7 +172,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Administrator:</t>
+          <t>ray chen:</t>
         </r>
         <r>
           <rPr>
@@ -191,7 +192,258 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
+          <t>不包含交易费</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
           <t>单价就是成交价，不包含交易费</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="BH9" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ray chen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+42.7</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>港币</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>*0.9369</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AT13" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ray chen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>不包含交易费</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AU19" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ray chen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>美团</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> -100</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AV19" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ray chen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>京东</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> -50
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>美团</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> -50</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z23" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ray chen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1411+192</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>（京东）</t>
         </r>
       </text>
     </comment>
@@ -200,7 +452,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>中国平安</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -423,6 +675,636 @@
       </rPr>
       <t>)</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>16.03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(19.56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>380.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(464</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>379</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(462.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>373.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(456.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>367.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(450.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>15.19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(18.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>371.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(455.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>356.08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(435.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洋河股份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>350.14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(428.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五粮液</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(13.22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>247.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(303.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港币</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>283.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港币</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>199.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(215.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>港币</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -515,7 +1397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -529,12 +1411,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -823,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:BM49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -832,9 +1730,20 @@
     <col min="6" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="19.5" customWidth="1"/>
     <col min="8" max="8" width="21.375" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="17.875" customWidth="1"/>
+    <col min="13" max="13" width="17.375" customWidth="1"/>
+    <col min="14" max="14" width="17.25" customWidth="1"/>
+    <col min="15" max="20" width="17.625" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="16.75" customWidth="1"/>
+    <col min="23" max="60" width="18.75" customWidth="1"/>
+    <col min="61" max="61" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1">
+    <row r="1" spans="1:63" s="2" customFormat="1">
       <c r="C1" s="2">
         <v>20211015</v>
       </c>
@@ -853,9 +1762,171 @@
       <c r="H1" s="2">
         <v>20211110</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="I1" s="2">
+        <v>20211124</v>
+      </c>
+      <c r="J1" s="2">
+        <v>20211126</v>
+      </c>
+      <c r="K1" s="2">
+        <v>20211129</v>
+      </c>
+      <c r="L1" s="2">
+        <v>20211130</v>
+      </c>
+      <c r="M1" s="2">
+        <v>20211206</v>
+      </c>
+      <c r="N1" s="2">
+        <v>20211214</v>
+      </c>
+      <c r="O1" s="2">
+        <v>20211215</v>
+      </c>
+      <c r="P1" s="2">
+        <v>20211220</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>20211231</v>
+      </c>
+      <c r="R1" s="2">
+        <v>20220106</v>
+      </c>
+      <c r="S1" s="2">
+        <v>20220111</v>
+      </c>
+      <c r="T1" s="2">
+        <v>20220113</v>
+      </c>
+      <c r="U1" s="2">
+        <v>20220128</v>
+      </c>
+      <c r="V1" s="2">
+        <v>20220308</v>
+      </c>
+      <c r="W1" s="2">
+        <v>20220315</v>
+      </c>
+      <c r="X1" s="2">
+        <v>20220407</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>20220425</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>20220607</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>20220617</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>20220621</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>20220628</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>20220707</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>20220715</v>
+      </c>
+      <c r="AF1" s="2">
+        <v>20220802</v>
+      </c>
+      <c r="AG1" s="2">
+        <v>20220804</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>20221019</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>20221026</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>20221031</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>20230110</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>20230224</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>20230525</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>20230531</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>20230606</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>20230613</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>20230620</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>20230626</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>20230808</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>20240423</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>20240424</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>20240425</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>20240603</v>
+      </c>
+      <c r="AX1" s="2">
+        <v>20240625</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>20240627</v>
+      </c>
+      <c r="AZ1" s="2">
+        <v>20240711</v>
+      </c>
+      <c r="BA1" s="2">
+        <v>20240725</v>
+      </c>
+      <c r="BB1" s="2">
+        <v>20240827</v>
+      </c>
+      <c r="BC1" s="2">
+        <v>20241017</v>
+      </c>
+      <c r="BD1" s="2">
+        <v>20241022</v>
+      </c>
+      <c r="BE1" s="2">
+        <v>20250116</v>
+      </c>
+      <c r="BF1" s="2">
+        <v>20250122</v>
+      </c>
+      <c r="BG1" s="2">
+        <v>20250124</v>
+      </c>
+      <c r="BH1" s="2">
+        <v>20240207</v>
+      </c>
+      <c r="BJ1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="BK1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:63">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -867,9 +1938,13 @@
       <c r="H2">
         <v>9725.19</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5"/>
+      <c r="BJ2">
+        <f>SUM(C2:BI2)</f>
+        <v>14710.29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:63">
+      <c r="A3" s="11"/>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -880,8 +1955,8 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5"/>
+    <row r="4" spans="1:63">
+      <c r="A4" s="11"/>
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,8 +1967,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="5"/>
+    <row r="5" spans="1:63">
+      <c r="A5" s="11"/>
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
@@ -904,238 +1979,833 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+    <row r="6" spans="1:63">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA6">
+        <v>450</v>
+      </c>
+      <c r="AH6">
+        <v>276</v>
+      </c>
+      <c r="AP6">
+        <v>450</v>
+      </c>
+      <c r="BA6">
+        <v>450</v>
+      </c>
+      <c r="BC6">
+        <v>279</v>
+      </c>
+      <c r="BK6">
+        <f>SUM(C6:BJ6)</f>
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="7" spans="1:63">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:63">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>10394.36</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="6"/>
-      <c r="B8" s="3" t="s">
+      <c r="H8">
+        <v>9912.27</v>
+      </c>
+      <c r="I8">
+        <v>16065.79</v>
+      </c>
+      <c r="N8">
+        <v>9132.6</v>
+      </c>
+      <c r="V8">
+        <v>2149.6799999999998</v>
+      </c>
+      <c r="BH8">
+        <v>-39936.93</v>
+      </c>
+      <c r="BJ8">
+        <f>SUM(C8:BI8)</f>
+        <v>7717.7699999999968</v>
+      </c>
+    </row>
+    <row r="9" spans="1:63">
+      <c r="A9" s="10"/>
+      <c r="B9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="3" t="s">
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" t="s">
+        <v>19</v>
+      </c>
+      <c r="V9" t="s">
+        <v>26</v>
+      </c>
+      <c r="BH9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:63">
+      <c r="A10" s="10"/>
+      <c r="B10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>600</v>
       </c>
-      <c r="H9">
+      <c r="H10">
         <v>600</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="6"/>
-      <c r="B10" s="3" t="s">
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="N10">
+        <v>600</v>
+      </c>
+      <c r="V10">
+        <v>200</v>
+      </c>
+      <c r="BH10">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:63">
+      <c r="A11" s="10"/>
+      <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>21.93</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
+      <c r="H11">
+        <v>20.69</v>
+      </c>
+      <c r="I11">
+        <v>32.57</v>
+      </c>
+      <c r="N11">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="V11">
+        <v>9.86</v>
+      </c>
+      <c r="BH11">
+        <v>69.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:63">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:63">
+      <c r="A13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>21278</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="3" t="s">
+      <c r="I13">
+        <v>11365</v>
+      </c>
+      <c r="L13">
+        <v>7716</v>
+      </c>
+      <c r="Y13">
+        <v>5355</v>
+      </c>
+      <c r="AJ13">
+        <v>3429</v>
+      </c>
+      <c r="AT13">
+        <v>-52611.29</v>
+      </c>
+      <c r="BJ13">
+        <f>SUM(C13:BI13)</f>
+        <v>-3468.2900000000009</v>
+      </c>
+    </row>
+    <row r="14" spans="1:63">
+      <c r="A14" s="10"/>
+      <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>7.09</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="6"/>
-      <c r="B14" s="3" t="s">
+      <c r="I14">
+        <v>7.1</v>
+      </c>
+      <c r="L14">
+        <v>7.01</v>
+      </c>
+      <c r="Y14">
+        <v>5.35</v>
+      </c>
+      <c r="AJ14">
+        <v>4.28</v>
+      </c>
+      <c r="AT14">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:63">
+      <c r="A15" s="10"/>
+      <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14">
+      <c r="E15">
         <v>3000</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="6"/>
-      <c r="B15" s="3" t="s">
+      <c r="I15">
+        <v>1600</v>
+      </c>
+      <c r="L15">
+        <v>1100</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>800</v>
+      </c>
+      <c r="AT15" s="8">
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:63">
+      <c r="A16" s="10"/>
+      <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6" t="s">
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <v>5</v>
+      </c>
+      <c r="Y16">
+        <v>5</v>
+      </c>
+      <c r="AJ16">
+        <v>5</v>
+      </c>
+      <c r="AT16" s="9">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:63">
+      <c r="A17" s="10"/>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF17">
+        <v>871</v>
+      </c>
+      <c r="AK17">
+        <v>1050</v>
+      </c>
+      <c r="BK17">
+        <f>SUM(C17:BJ17)</f>
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="18" spans="1:63">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:63">
+      <c r="A19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F17">
+      <c r="F19">
         <v>39797.839999999997</v>
       </c>
-      <c r="G17">
+      <c r="G19">
         <v>38388</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="3" t="s">
+      <c r="J19">
+        <v>114332.77</v>
+      </c>
+      <c r="K19">
+        <v>75956.17</v>
+      </c>
+      <c r="L19">
+        <v>37453.65</v>
+      </c>
+      <c r="M19">
+        <v>36891.230000000003</v>
+      </c>
+      <c r="O19">
+        <v>37233.24</v>
+      </c>
+      <c r="P19">
+        <v>35682.17</v>
+      </c>
+      <c r="R19">
+        <v>35088.51</v>
+      </c>
+      <c r="W19">
+        <v>24756.44</v>
+      </c>
+      <c r="AE19">
+        <v>28449.95</v>
+      </c>
+      <c r="AI19">
+        <v>19968.43</v>
+      </c>
+      <c r="AU19">
+        <v>-9341</v>
+      </c>
+      <c r="AV19">
+        <v>-9732</v>
+      </c>
+      <c r="BJ19">
+        <f>SUM(C19:BI19)</f>
+        <v>504925.39999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:63">
+      <c r="A20" s="10"/>
+      <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="3" t="s">
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
+        <v>24</v>
+      </c>
+      <c r="W20" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="1"/>
+      <c r="AU20" s="1"/>
+      <c r="AV20" s="1"/>
+      <c r="AW20" s="1"/>
+      <c r="AX20" s="1"/>
+      <c r="AY20" s="1"/>
+      <c r="AZ20" s="1"/>
+      <c r="BA20" s="1"/>
+      <c r="BB20" s="1"/>
+      <c r="BC20" s="1"/>
+      <c r="BD20" s="1"/>
+      <c r="BE20" s="1"/>
+      <c r="BF20" s="1"/>
+      <c r="BG20" s="1"/>
+      <c r="BH20" s="1"/>
+    </row>
+    <row r="21" spans="1:63">
+      <c r="A21" s="10"/>
+      <c r="B21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F19">
+      <c r="F21">
         <v>100</v>
       </c>
-      <c r="G19">
+      <c r="G21">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="3" t="s">
+      <c r="J21">
+        <v>300</v>
+      </c>
+      <c r="K21">
+        <v>200</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="AE21">
+        <v>100</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:63">
+      <c r="A22" s="10"/>
+      <c r="B22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F20">
+      <c r="F22">
         <v>77.27</v>
       </c>
-      <c r="G20">
+      <c r="G22">
         <v>74.78</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1185.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="J22">
+        <v>220.92</v>
+      </c>
+      <c r="K22">
+        <v>146.34</v>
+      </c>
+      <c r="L22">
+        <v>73.16</v>
+      </c>
+      <c r="M22">
+        <v>71.98</v>
+      </c>
+      <c r="O22">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="P22">
+        <v>69.650000000000006</v>
+      </c>
+      <c r="R22">
+        <v>68.45</v>
+      </c>
+      <c r="W22">
+        <v>49.04</v>
+      </c>
+      <c r="AE22">
+        <v>55.75</v>
+      </c>
+      <c r="AI22">
+        <v>39.74</v>
+      </c>
+      <c r="AU22">
+        <v>19</v>
+      </c>
+      <c r="AV22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:63">
       <c r="A23" s="6"/>
       <c r="B23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z23">
+        <v>1603</v>
+      </c>
+      <c r="AO23">
+        <v>2606.4</v>
+      </c>
+      <c r="AU23">
+        <v>125.66</v>
+      </c>
+      <c r="AW23">
+        <v>3781.75</v>
+      </c>
+      <c r="BK23">
+        <f>SUM(C23:BJ23)</f>
+        <v>8116.8099999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:63">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:63">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1185.02</v>
+      </c>
+      <c r="BJ25">
+        <f>SUM(G25)</f>
+        <v>1185.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:63">
+      <c r="A26" s="10"/>
+      <c r="B26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G23">
+      <c r="G26">
         <v>11.8</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="3" t="s">
+    <row r="27" spans="1:63">
+      <c r="A27" s="10"/>
+      <c r="B27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24">
+      <c r="G27">
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="3" t="s">
+    <row r="28" spans="1:63">
+      <c r="A28" s="10"/>
+      <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6" t="s">
+    <row r="29" spans="1:63">
+      <c r="A29" s="7"/>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD29">
+        <v>135</v>
+      </c>
+      <c r="AY29">
+        <v>131.5</v>
+      </c>
+      <c r="BD29">
+        <v>10.9</v>
+      </c>
+      <c r="BE29">
+        <v>10.3</v>
+      </c>
+      <c r="BK29">
+        <f>SUM(C29:BJ29)</f>
+        <v>287.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:63">
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:63">
+      <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H27">
+      <c r="H31">
         <v>10295</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="3" t="s">
+      <c r="BJ31">
+        <f>SUM(C31:BI31)</f>
+        <v>10295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:63">
+      <c r="A32" s="10"/>
+      <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H28">
+      <c r="H32">
         <v>34.299999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="3" t="s">
+    <row r="33" spans="1:65">
+      <c r="A33" s="10"/>
+      <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H29">
+      <c r="H33">
         <v>300</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="3" t="s">
+    <row r="34" spans="1:65">
+      <c r="A34" s="10"/>
+      <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H30">
+      <c r="H34">
         <v>5</v>
       </c>
     </row>
+    <row r="35" spans="1:65">
+      <c r="A35" s="6"/>
+      <c r="B35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X35">
+        <v>300</v>
+      </c>
+      <c r="AG35">
+        <v>600</v>
+      </c>
+      <c r="AL35">
+        <v>300</v>
+      </c>
+      <c r="AS35">
+        <v>300</v>
+      </c>
+      <c r="BK35">
+        <f>SUM(C35:BJ35)</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:65">
+      <c r="A37" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>16606</v>
+      </c>
+      <c r="S37">
+        <v>16315</v>
+      </c>
+      <c r="T37">
+        <v>15687</v>
+      </c>
+      <c r="AM37">
+        <v>13855</v>
+      </c>
+      <c r="AN37">
+        <v>13515</v>
+      </c>
+      <c r="BJ37">
+        <f>SUM(C37:BI37)</f>
+        <v>75978</v>
+      </c>
+    </row>
+    <row r="38" spans="1:65">
+      <c r="A38" s="10"/>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q38">
+        <v>166.01</v>
+      </c>
+      <c r="S38">
+        <v>163.1</v>
+      </c>
+      <c r="T38">
+        <v>156.82</v>
+      </c>
+      <c r="AM38">
+        <v>138.5</v>
+      </c>
+      <c r="AN38">
+        <v>135.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:65">
+      <c r="A39" s="10"/>
+      <c r="B39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
+        <v>100</v>
+      </c>
+      <c r="AM39">
+        <v>100</v>
+      </c>
+      <c r="AN39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:65">
+      <c r="A40" s="10"/>
+      <c r="B40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q40">
+        <v>5</v>
+      </c>
+      <c r="S40">
+        <v>5</v>
+      </c>
+      <c r="T40">
+        <v>5</v>
+      </c>
+      <c r="AM40">
+        <v>5</v>
+      </c>
+      <c r="AN40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:65">
+      <c r="A41" s="6"/>
+      <c r="B41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB41">
+        <v>900</v>
+      </c>
+      <c r="AQ41">
+        <v>1870</v>
+      </c>
+      <c r="AX41">
+        <v>2330</v>
+      </c>
+      <c r="BB41">
+        <v>714</v>
+      </c>
+      <c r="BG41">
+        <v>1165</v>
+      </c>
+      <c r="BK41">
+        <f>SUM(C41:BJ41)</f>
+        <v>6979</v>
+      </c>
+    </row>
+    <row r="43" spans="1:65">
+      <c r="A43" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="U43">
+        <v>19915</v>
+      </c>
+      <c r="BJ43">
+        <f>SUM(C43:BI43)</f>
+        <v>19915</v>
+      </c>
+    </row>
+    <row r="44" spans="1:65">
+      <c r="A44" s="10"/>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U44">
+        <v>199.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:65">
+      <c r="A45" s="10"/>
+      <c r="B45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:65">
+      <c r="A46" s="10"/>
+      <c r="B46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:65">
+      <c r="A47" s="7"/>
+      <c r="B47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC47">
+        <v>302</v>
+      </c>
+      <c r="AR47">
+        <v>378.2</v>
+      </c>
+      <c r="AZ47">
+        <v>467</v>
+      </c>
+      <c r="BF47">
+        <v>257.60000000000002</v>
+      </c>
+      <c r="BK47">
+        <f>SUM(C47:BJ47)</f>
+        <v>1404.8000000000002</v>
+      </c>
+      <c r="BM47" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="62:63">
+      <c r="BJ49">
+        <f>SUM(BJ2:BJ43)</f>
+        <v>631258.18999999994</v>
+      </c>
+      <c r="BK49">
+        <f>SUM(BK6:BK47)</f>
+        <v>22114.31</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A27:A30"/>
+  <mergeCells count="8">
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A13:A17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
